--- a/data/gravel/Bearclaw Buck Macho 2025.xlsx
+++ b/data/gravel/Bearclaw Buck Macho 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A5C465-100B-DD45-96FB-4920BBA39658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFA26F-54FC-3049-8499-A771D76B4A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31700" yWindow="-26260" windowWidth="29540" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>a8:f32</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/BUCK-MACHO_2048x2048.jpg?v=1710938209</t>
   </si>
 </sst>
 </file>
@@ -778,6 +781,11 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Bearclaw Buck Macho 2025.xlsx
+++ b/data/gravel/Bearclaw Buck Macho 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFA26F-54FC-3049-8499-A771D76B4A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D0BE49-02F8-F947-B59E-F3482F40618E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31700" yWindow="-26260" windowWidth="29540" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/BUCK-MACHO_2048x2048.jpg?v=1710938209</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dexter, Michigan, USA</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1617,6 +1623,14 @@
         <v>76</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Bearclaw Buck Macho 2025.xlsx
+++ b/data/gravel/Bearclaw Buck Macho 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D0BE49-02F8-F947-B59E-F3482F40618E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB31D56D-DCBD-954B-8F48-B7FA442A9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31700" yWindow="-26260" windowWidth="29540" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>Dexter, Michigan, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -741,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1469,165 +1487,195 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>38</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B69">
-        <v>2490</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>2490</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>114</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>115</v>
       </c>
     </row>

--- a/data/gravel/Bearclaw Buck Macho 2025.xlsx
+++ b/data/gravel/Bearclaw Buck Macho 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB31D56D-DCBD-954B-8F48-B7FA442A9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18677957-6FAE-B84B-BFF4-3CB75F4D52B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31700" yWindow="-26260" windowWidth="29540" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5960" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -371,9 +371,6 @@
     <t>frame only</t>
   </si>
   <si>
-    <t>a8:f32</t>
-  </si>
-  <si>
     <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/BUCK-MACHO_2048x2048.jpg?v=1710938209</t>
   </si>
   <si>
@@ -399,6 +396,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
   </si>
 </sst>
 </file>
@@ -759,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -807,7 +813,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -815,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1175,40 +1181,51 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="A23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="4">
+        <v>120</v>
+      </c>
+      <c r="D23" s="4">
+        <v>120</v>
+      </c>
+      <c r="E23" s="4">
+        <v>120</v>
+      </c>
+      <c r="F23" s="4">
+        <v>120</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="A24" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>20</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1219,464 +1236,481 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29">
-        <v>2.5</v>
-      </c>
-      <c r="D29">
-        <v>2.5</v>
-      </c>
-      <c r="E29">
-        <v>2.5</v>
-      </c>
-      <c r="F29">
-        <v>2.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>2.5</v>
+      </c>
+      <c r="D31">
+        <v>2.5</v>
+      </c>
+      <c r="E31">
+        <v>2.5</v>
+      </c>
+      <c r="F31">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32">
+        <v>2.8</v>
+      </c>
+      <c r="D32">
+        <v>2.8</v>
+      </c>
+      <c r="E32">
+        <v>2.8</v>
+      </c>
+      <c r="F32">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:F32" si="2">D33*2.54</f>
+      <c r="D33">
+        <f t="shared" ref="D33:F34" si="2">D35*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="2"/>
         <v>177.8</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="2"/>
         <v>185.42000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>172.72</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <f t="shared" si="2"/>
         <v>187.96</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <f t="shared" si="2"/>
         <v>195.58</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C33">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>63</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>67</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>70</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F35" s="5">
         <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>68</v>
-      </c>
-      <c r="D34">
-        <v>71</v>
-      </c>
-      <c r="E34">
-        <v>74</v>
-      </c>
-      <c r="F34">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>68</v>
+      </c>
+      <c r="D36">
+        <v>71</v>
+      </c>
+      <c r="E36">
+        <v>74</v>
+      </c>
+      <c r="F36">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" t="s">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40">
-        <v>20</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>110</v>
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <v>2.8</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>20</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43">
-        <v>120</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B46">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59">
-        <v>38</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="B61">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>2490</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>2490</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" t="s">
         <v>114</v>
-      </c>
-      <c r="B79" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Bearclaw Buck Macho 2025.xlsx
+++ b/data/gravel/Bearclaw Buck Macho 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18677957-6FAE-B84B-BFF4-3CB75F4D52B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B46B0B-A111-2348-AC4C-2195EC0D6F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5960" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -251,9 +251,6 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>a8:f34</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -808,12 +808,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -829,19 +829,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -852,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="4">
         <v>592</v>
@@ -875,7 +875,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4">
         <v>66</v>
@@ -898,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4">
         <v>105</v>
@@ -921,7 +921,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4">
         <v>75</v>
@@ -944,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4">
         <v>390</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4">
         <v>727.7</v>
@@ -990,7 +990,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <f>VALUE(LEFT(G15,3))</f>
@@ -1009,16 +1009,16 @@
         <v>425</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1026,7 +1026,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1">
         <f>VALUE(LEFT(G16,4))</f>
@@ -1045,16 +1045,16 @@
         <v>1218</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1062,7 +1062,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4">
         <v>70</v>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="4">
         <v>531</v>
@@ -1108,7 +1108,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4">
         <v>44</v>
@@ -1131,7 +1131,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="4">
         <v>644</v>
@@ -1154,7 +1154,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="4">
         <v>420</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C23" s="4">
         <v>120</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1397,22 +1397,22 @@
         <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -1420,15 +1420,15 @@
         <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>71</v>
       </c>
-      <c r="B39" t="s">
-        <v>72</v>
+      <c r="B39" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -1461,7 +1461,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -1521,32 +1521,32 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1554,7 +1554,7 @@
         <v>45</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1608,7 +1608,7 @@
         <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1616,7 +1616,7 @@
         <v>55</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1672,7 +1672,7 @@
         <v>64</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1683,7 +1683,7 @@
         <v>2490</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1702,15 +1702,15 @@
         <v>68</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" t="s">
         <v>113</v>
-      </c>
-      <c r="B81" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
